--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:15</t>
+    <t xml:space="preserve">2026-09-24 01:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -710,7 +710,7 @@
         <v>0.07</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="10">
@@ -750,13 +750,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>-0.13</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="12">
@@ -1028,10 +1028,10 @@
         <v>0.65</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="25">
@@ -1071,13 +1071,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.82</v>
+        <v>-0.84</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>-0.13</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="27">
@@ -1322,11 +1322,15 @@
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" s="2" t="n">
+        <v>0.72</v>
+      </c>
       <c r="F38" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="G38" s="2"/>
+      <c r="G38" s="2" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
@@ -1341,11 +1345,15 @@
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" s="2" t="n">
+        <v>0.81</v>
+      </c>
       <c r="F39" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G39" s="2"/>
+        <v>0.11</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
@@ -1360,11 +1368,15 @@
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="2"/>
+      <c r="E40" s="2" t="n">
+        <v>0.09</v>
+      </c>
       <c r="F40" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="G40" s="2"/>
+      <c r="G40" s="2" t="n">
+        <v>-0.12</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
@@ -1379,11 +1391,15 @@
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E41" s="2"/>
+      <c r="E41" s="2" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="F41" s="2" t="n">
         <v>0.11</v>
       </c>
-      <c r="G41" s="2"/>
+      <c r="G41" s="2" t="n">
+        <v>-0.46</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
@@ -1421,11 +1437,15 @@
       <c r="D43" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" s="2" t="n">
+        <v>-0.93</v>
+      </c>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G43" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>-0.93</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
@@ -1440,11 +1460,15 @@
       <c r="D44" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F44" s="2" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="G44" s="2"/>
+        <v>-0.29</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1.24</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
@@ -1459,11 +1483,15 @@
       <c r="D45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" s="2" t="n">
+        <v>-0.46</v>
+      </c>
       <c r="F45" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="G45" s="2"/>
+      <c r="G45" s="2" t="n">
+        <v>-0.65</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
@@ -1615,11 +1643,15 @@
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="2"/>
+      <c r="E53" s="2" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F53" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="G53" s="2"/>
+      <c r="G53" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
@@ -1634,11 +1666,15 @@
       <c r="D54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E54" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F54" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G54" s="2"/>
+      <c r="G54" s="2" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
@@ -1653,11 +1689,15 @@
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="2"/>
+      <c r="E55" s="2" t="n">
+        <v>-0.47</v>
+      </c>
       <c r="F55" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="G55" s="2"/>
+      <c r="G55" s="2" t="n">
+        <v>-0.65</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
@@ -1672,11 +1712,15 @@
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E56" s="2"/>
+      <c r="E56" s="2" t="n">
+        <v>-0.8</v>
+      </c>
       <c r="F56" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G56" s="2"/>
+        <v>0.07</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>-0.88</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
@@ -1714,11 +1758,15 @@
       <c r="D58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" s="2" t="n">
+        <v>-0.93</v>
+      </c>
       <c r="F58" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="G58" s="2"/>
+      <c r="G58" s="2" t="n">
+        <v>-0.97</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
@@ -1733,11 +1781,15 @@
       <c r="D59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" s="2" t="n">
+        <v>0.72</v>
+      </c>
       <c r="F59" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="G59" s="2"/>
+        <v>-0.27</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
@@ -1752,11 +1804,15 @@
       <c r="D60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" s="2" t="n">
+        <v>-0.61</v>
+      </c>
       <c r="F60" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="G60" s="2"/>
+      <c r="G60" s="2" t="n">
+        <v>-0.74</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
@@ -1978,13 +2034,13 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="F71" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G71" s="2" t="n">
         <v>0.25</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>0.27</v>
       </c>
     </row>
     <row r="72">
@@ -2233,10 +2289,10 @@
         <v>-0.46</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="84">
@@ -2256,10 +2312,10 @@
         <v>-0.01</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="85">
@@ -2299,13 +2355,13 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="87">
@@ -2551,13 +2607,13 @@
         <v>18</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.32</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.24</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="99">
@@ -2574,13 +2630,13 @@
         <v>18</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.56</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>-0.42</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="100">
@@ -2597,13 +2653,13 @@
         <v>18</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.52</v>
+        <v>0.29</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="101">
@@ -2620,13 +2676,13 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="102">
@@ -2666,13 +2722,13 @@
         <v>24</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.37</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="104">
@@ -2689,13 +2745,13 @@
         <v>24</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.7</v>
+        <v>0.08</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.58</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="105">
@@ -2712,13 +2768,13 @@
         <v>24</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>-0.09</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="106">
@@ -2872,13 +2928,13 @@
         <v>18</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="114">
@@ -2895,13 +2951,13 @@
         <v>18</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="115">
@@ -2918,13 +2974,13 @@
         <v>18</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>-0.12</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="116">
@@ -2941,13 +2997,13 @@
         <v>18</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="117">
@@ -2987,13 +3043,13 @@
         <v>24</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>-0.2</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="119">
@@ -3010,13 +3066,13 @@
         <v>24</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.69</v>
+        <v>0.46</v>
       </c>
       <c r="F119" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.51</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="120">
@@ -3033,13 +3089,13 @@
         <v>24</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>-0.1</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="121">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_magallanes.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:05</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
